--- a/data/stx_xlsx/EG7.ST.xlsx
+++ b/data/stx_xlsx/EG7.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="362">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -694,6 +694,9 @@
   </si>
   <si>
     <t>Bond Loans</t>
+  </si>
+  <si>
+    <t>Liabilities to credit institutions (Do not use)</t>
   </si>
   <si>
     <t>Deferred tax liability</t>
@@ -1233,7 +1236,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1320,6 +1323,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -8236,8 +8242,8 @@
       <c r="M80" s="22"/>
     </row>
     <row r="81" ht="15.0" customHeight="1">
-      <c r="A81" s="14" t="s">
-        <v>172</v>
+      <c r="A81" s="29" t="s">
+        <v>225</v>
       </c>
       <c r="B81" s="15">
         <v>379.32</v>
@@ -8299,7 +8305,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B83" s="16">
         <v>87.15</v>
@@ -8332,7 +8338,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B84" s="16">
         <v>85.95</v>
@@ -8363,7 +8369,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B85" s="22"/>
       <c r="C85" s="16">
@@ -8392,7 +8398,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B86" s="16">
         <v>2.95</v>
@@ -8423,7 +8429,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B87" s="22"/>
       <c r="C87" s="22"/>
@@ -8442,7 +8448,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B88" s="16">
         <v>0.11</v>
@@ -8467,7 +8473,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B89" s="18">
         <v>592.77</v>
@@ -8587,7 +8593,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B93" s="16">
         <v>23.95</v>
@@ -8628,7 +8634,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B94" s="16">
         <v>20.89</v>
@@ -8669,7 +8675,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B95" s="16">
         <v>54.35</v>
@@ -8700,7 +8706,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B96" s="16">
         <v>20.12</v>
@@ -8741,7 +8747,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B97" s="22"/>
       <c r="C97" s="22"/>
@@ -8760,7 +8766,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B98" s="15">
         <v>116.13</v>
@@ -8791,7 +8797,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B99" s="15">
         <v>236.63</v>
@@ -8832,7 +8838,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B100" s="22"/>
       <c r="C100" s="16">
@@ -8855,7 +8861,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B101" s="22"/>
       <c r="C101" s="16">
@@ -8878,7 +8884,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B102" s="22"/>
       <c r="C102" s="15">
@@ -8901,7 +8907,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B103" s="20">
         <v>-0.11</v>
@@ -8922,7 +8928,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B104" s="18">
         <v>495.34</v>
@@ -8963,7 +8969,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B105" s="18">
         <v>1088.11</v>
@@ -9004,7 +9010,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B106" s="20">
         <v>-0.11</v>
@@ -9029,7 +9035,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B107" s="18">
         <v>2767.89</v>
@@ -9070,7 +9076,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B108" s="22">
         <v>0.0</v>
@@ -9111,7 +9117,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B109" s="16">
         <v>88.6</v>
@@ -9152,7 +9158,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B110" s="16">
         <v>88.6</v>
@@ -9193,7 +9199,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B111" s="22"/>
       <c r="C111" s="16">
@@ -9216,7 +9222,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B112" s="22"/>
       <c r="C112" s="16">
@@ -9239,7 +9245,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B113" s="22"/>
       <c r="C113" s="16">
@@ -9262,7 +9268,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B114" s="22"/>
       <c r="C114" s="22"/>
@@ -9281,7 +9287,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B115" s="22"/>
       <c r="C115" s="16">
@@ -9304,7 +9310,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B116" s="22"/>
       <c r="C116" s="16">
@@ -9325,7 +9331,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B117" s="22"/>
       <c r="C117" s="16">
@@ -9344,7 +9350,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B118" s="22"/>
       <c r="C118" s="16">
@@ -9365,7 +9371,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B119" s="16">
         <v>88.6</v>
@@ -9406,7 +9412,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B120" s="16">
         <v>1.0</v>
@@ -9447,7 +9453,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B121" s="16">
         <v>88.6</v>
@@ -9488,7 +9494,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B122" s="22">
         <v>0.0</v>
@@ -9529,7 +9535,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B123" s="15">
         <v>550.0</v>
@@ -9554,7 +9560,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B124" s="22"/>
       <c r="C124" s="22"/>
@@ -9573,7 +9579,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B125" s="22"/>
       <c r="C125" s="22"/>
@@ -9592,7 +9598,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B126" s="22"/>
       <c r="C126" s="22"/>
@@ -9611,7 +9617,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B127" s="22"/>
       <c r="C127" s="22"/>
@@ -10523,7 +10529,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10753,34 +10759,34 @@
         <v>34</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -10820,7 +10826,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -10870,7 +10876,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="16">
@@ -10893,7 +10899,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="20">
@@ -10910,7 +10916,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="21">
@@ -10935,7 +10941,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B23" s="15">
         <v>2441.79</v>
@@ -10962,7 +10968,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B24" s="22">
         <v>0.0</v>
@@ -10981,7 +10987,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B25" s="15">
         <v>186.73</v>
@@ -11014,7 +11020,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" s="21">
         <v>-2209.84</v>
@@ -11082,7 +11088,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B28" s="20">
         <v>-45.23</v>
@@ -11117,7 +11123,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -11136,7 +11142,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="16">
@@ -11163,7 +11169,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B31" s="22"/>
       <c r="C31" s="20">
@@ -11194,7 +11200,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B32" s="22"/>
       <c r="C32" s="16">
@@ -11221,7 +11227,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B33" s="22"/>
       <c r="C33" s="16">
@@ -11254,7 +11260,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B34" s="22"/>
       <c r="C34" s="20">
@@ -11287,7 +11293,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B35" s="20">
         <v>-59.21</v>
@@ -11304,7 +11310,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -11325,7 +11331,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B37" s="18">
         <v>127.52</v>
@@ -11360,7 +11366,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B38" s="20">
         <v>-6.46</v>
@@ -11391,7 +11397,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B39" s="21">
         <v>-299.0</v>
@@ -11426,7 +11432,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B40" s="20">
         <v>-22.45</v>
@@ -11457,7 +11463,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B41" s="22">
         <v>0.0</v>
@@ -11476,7 +11482,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B42" s="22"/>
       <c r="C42" s="16">
@@ -11499,7 +11505,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
@@ -11522,7 +11528,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -11541,7 +11547,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
@@ -11560,7 +11566,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B46" s="22"/>
       <c r="C46" s="22"/>
@@ -11579,7 +11585,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B47" s="25">
         <v>-327.92</v>
@@ -11614,7 +11620,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B48" s="22"/>
       <c r="C48" s="22"/>
@@ -11639,7 +11645,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B49" s="22"/>
       <c r="C49" s="22"/>
@@ -11662,7 +11668,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B50" s="22"/>
       <c r="C50" s="22"/>
@@ -11685,7 +11691,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B51" s="22">
         <v>0.0</v>
@@ -11706,7 +11712,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -11723,7 +11729,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B53" s="15">
         <v>361.7</v>
@@ -11752,7 +11758,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B54" s="22"/>
       <c r="C54" s="22">
@@ -11777,7 +11783,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B55" s="20">
         <v>-31.03</v>
@@ -11804,7 +11810,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B56" s="20">
         <v>-0.11</v>
@@ -11823,7 +11829,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B57" s="20">
         <v>-18.64</v>
@@ -11840,7 +11846,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B58" s="18">
         <v>311.92</v>
@@ -11875,7 +11881,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B59" s="15">
         <v>351.55</v>
@@ -11910,7 +11916,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B60" s="15">
         <v>426.78</v>
@@ -11945,7 +11951,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B61" s="20">
         <v>-38.66</v>
@@ -11976,7 +11982,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B62" s="15">
         <v>111.53</v>
@@ -12007,7 +12013,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B63" s="19">
         <v>72.87</v>
@@ -12999,7 +13005,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -13315,7 +13321,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -13368,1054 +13374,1054 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>313</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
+      <c r="A20" s="30" t="s">
+        <v>314</v>
+      </c>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="B21" s="32">
+      <c r="A21" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="B21" s="33">
         <v>1225.22</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="33">
         <v>1285.85</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="33">
         <v>2090.36</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="33">
         <v>2948.59</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="33">
         <v>5313.29</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="33">
         <v>674.98</v>
       </c>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="31" t="s">
-        <v>314</v>
-      </c>
-      <c r="B22" s="32">
+      <c r="A22" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="B22" s="33">
         <v>2632.86</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="33">
         <v>2483.22</v>
       </c>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="29" t="s">
-        <v>315</v>
-      </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
+      <c r="A23" s="30" t="s">
+        <v>316</v>
+      </c>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="31" t="s">
-        <v>315</v>
-      </c>
-      <c r="B24" s="32">
+      <c r="A24" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="B24" s="33">
         <v>1484.81</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="33">
         <v>1685.93</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="33">
         <v>2335.18</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="33">
         <v>2970.71</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="33">
         <v>5836.95</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="33">
         <v>553.08</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="33">
         <v>165.9</v>
       </c>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="34"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="31" t="s">
-        <v>316</v>
-      </c>
-      <c r="B25" s="32">
+      <c r="A25" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="B25" s="33">
         <v>2927.76</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <v>2694.98</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="33">
         <v>2236.4</v>
       </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="29" t="s">
-        <v>317</v>
-      </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
+      <c r="A26" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="31" t="s">
-        <v>318</v>
-      </c>
-      <c r="B27" s="34">
+      <c r="A27" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="B27" s="35">
         <v>16.76</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="35">
         <v>19.03</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="35">
         <v>26.36</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="35">
         <v>34.1</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="33">
         <v>127.39</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="35">
         <v>17.72</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="35">
         <v>10.93</v>
       </c>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="31" t="s">
-        <v>319</v>
-      </c>
-      <c r="B28" s="34">
+      <c r="A28" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="B28" s="35">
         <v>45.28</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="35">
         <v>44.86</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="35">
         <v>40.49</v>
       </c>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>320</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
+      <c r="A29" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="B30" s="35">
+      <c r="A30" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="B30" s="36">
         <v>-9.55</v>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="37">
         <v>11.39</v>
       </c>
-      <c r="D30" s="36">
+      <c r="D30" s="37">
         <v>7.06</v>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="36">
         <v>-1.16</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="36">
         <v>-4.51</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="36">
         <v>-5.44</v>
       </c>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="36"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="37"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="31" t="s">
-        <v>322</v>
-      </c>
-      <c r="B31" s="35">
+      <c r="A31" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="B31" s="36">
         <v>-1.51</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="36">
         <v>-1.26</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="36"/>
-      <c r="K31" s="36"/>
-      <c r="L31" s="36"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="37"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="29" t="s">
-        <v>323</v>
-      </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
+      <c r="A32" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="31" t="s">
-        <v>324</v>
-      </c>
-      <c r="B33" s="36">
+      <c r="A33" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="B33" s="37">
         <v>0.0</v>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="37">
         <v>1.67</v>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="37">
         <v>0.0</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="37">
         <v>0.0</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="37">
         <v>0.0</v>
       </c>
-      <c r="G33" s="36">
+      <c r="G33" s="37">
         <v>0.0</v>
       </c>
-      <c r="H33" s="36">
+      <c r="H33" s="37">
         <v>0.0</v>
       </c>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="36"/>
-      <c r="L33" s="36"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="37"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="B34" s="36">
+      <c r="A34" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="B34" s="37">
         <v>0.14</v>
       </c>
-      <c r="C34" s="36">
+      <c r="C34" s="37">
         <v>0.14</v>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="37">
         <v>0.0</v>
       </c>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="B35" s="36">
+      <c r="A35" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="B35" s="37">
         <v>0.0</v>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="37">
         <v>2.38</v>
       </c>
-      <c r="D35" s="36">
+      <c r="D35" s="37">
         <v>0.0</v>
       </c>
-      <c r="E35" s="36">
+      <c r="E35" s="37">
         <v>0.0</v>
       </c>
-      <c r="F35" s="36">
+      <c r="F35" s="37">
         <v>0.0</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <v>0.0</v>
       </c>
-      <c r="H35" s="36">
+      <c r="H35" s="37">
         <v>0.0</v>
       </c>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="36"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="37"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="31" t="s">
-        <v>327</v>
-      </c>
-      <c r="B36" s="36">
+      <c r="A36" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="B36" s="37">
         <v>0.2</v>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="37">
         <v>0.2</v>
       </c>
-      <c r="D36" s="36">
+      <c r="D36" s="37">
         <v>0.0</v>
       </c>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
-      <c r="J36" s="36"/>
-      <c r="K36" s="36"/>
-      <c r="L36" s="36"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="37"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="37"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
+      <c r="A37" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="31" t="s">
-        <v>329</v>
-      </c>
-      <c r="B38" s="34">
+      <c r="A38" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="B38" s="35">
         <v>0.36</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="35">
         <v>0.43</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="35">
         <v>0.64</v>
       </c>
-      <c r="E38" s="34">
+      <c r="E38" s="35">
         <v>0.66</v>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="35">
         <v>3.01</v>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="35">
         <v>3.61</v>
       </c>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="33"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="34"/>
+      <c r="J38" s="34"/>
+      <c r="K38" s="34"/>
+      <c r="L38" s="34"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="31" t="s">
-        <v>330</v>
-      </c>
-      <c r="B39" s="34">
+      <c r="A39" s="32" t="s">
+        <v>331</v>
+      </c>
+      <c r="B39" s="35">
         <v>0.97</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="35">
         <v>1.19</v>
       </c>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="33"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="34"/>
+      <c r="L39" s="34"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="29" t="s">
-        <v>331</v>
-      </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
+      <c r="A40" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="31" t="s">
-        <v>332</v>
-      </c>
-      <c r="B41" s="33"/>
-      <c r="C41" s="34">
+      <c r="A41" s="32" t="s">
+        <v>333</v>
+      </c>
+      <c r="B41" s="34"/>
+      <c r="C41" s="35">
         <v>32.84</v>
       </c>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="33"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="34"/>
+      <c r="L41" s="34"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="29" t="s">
-        <v>333</v>
-      </c>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
+      <c r="A42" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="31" t="s">
-        <v>334</v>
-      </c>
-      <c r="B43" s="34">
+      <c r="A43" s="32" t="s">
+        <v>335</v>
+      </c>
+      <c r="B43" s="35">
         <v>0.84</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="35">
         <v>0.82</v>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="35">
         <v>1.32</v>
       </c>
-      <c r="E43" s="34">
+      <c r="E43" s="35">
         <v>2.04</v>
       </c>
-      <c r="F43" s="34">
+      <c r="F43" s="35">
         <v>8.49</v>
       </c>
-      <c r="G43" s="34">
+      <c r="G43" s="35">
         <v>3.89</v>
       </c>
-      <c r="H43" s="34">
+      <c r="H43" s="35">
         <v>3.1</v>
       </c>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="33"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="34"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="31" t="s">
-        <v>335</v>
-      </c>
-      <c r="B44" s="34">
+      <c r="A44" s="32" t="s">
+        <v>336</v>
+      </c>
+      <c r="B44" s="35">
         <v>2.32</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="35">
         <v>2.76</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="35">
         <v>3.52</v>
       </c>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="33"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
+      <c r="K44" s="34"/>
+      <c r="L44" s="34"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="29" t="s">
-        <v>336</v>
-      </c>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
-      <c r="K45" s="30"/>
-      <c r="L45" s="30"/>
+      <c r="A45" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="31"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="B46" s="33"/>
-      <c r="C46" s="34">
+      <c r="A46" s="32" t="s">
+        <v>338</v>
+      </c>
+      <c r="B46" s="34"/>
+      <c r="C46" s="35">
         <v>8.78</v>
       </c>
-      <c r="D46" s="34">
+      <c r="D46" s="35">
         <v>14.16</v>
       </c>
-      <c r="E46" s="32">
+      <c r="E46" s="33">
         <v>711.42</v>
       </c>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="33"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
+      <c r="J46" s="34"/>
+      <c r="K46" s="34"/>
+      <c r="L46" s="34"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="31" t="s">
-        <v>338</v>
-      </c>
-      <c r="B47" s="33"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="33"/>
+      <c r="A47" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="B47" s="34"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+      <c r="J47" s="34"/>
+      <c r="K47" s="34"/>
+      <c r="L47" s="34"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="29" t="s">
-        <v>339</v>
-      </c>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="30"/>
-      <c r="J48" s="30"/>
-      <c r="K48" s="30"/>
-      <c r="L48" s="30"/>
+      <c r="A48" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="31"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="B49" s="32">
+      <c r="A49" s="32" t="s">
+        <v>341</v>
+      </c>
+      <c r="B49" s="33">
         <v>1312.94</v>
       </c>
-      <c r="C49" s="34">
+      <c r="C49" s="35">
         <v>4.46</v>
       </c>
-      <c r="D49" s="34">
+      <c r="D49" s="35">
         <v>5.12</v>
       </c>
-      <c r="E49" s="34">
+      <c r="E49" s="35">
         <v>5.43</v>
       </c>
-      <c r="F49" s="32">
+      <c r="F49" s="33">
         <v>488.87</v>
       </c>
-      <c r="G49" s="33"/>
-      <c r="H49" s="34">
+      <c r="G49" s="34"/>
+      <c r="H49" s="35">
         <v>49.15</v>
       </c>
-      <c r="I49" s="33"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="33"/>
-      <c r="L49" s="33"/>
+      <c r="I49" s="34"/>
+      <c r="J49" s="34"/>
+      <c r="K49" s="34"/>
+      <c r="L49" s="34"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="31" t="s">
-        <v>341</v>
-      </c>
-      <c r="B50" s="34">
+      <c r="A50" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="B50" s="35">
         <v>13.42</v>
       </c>
-      <c r="C50" s="34">
+      <c r="C50" s="35">
         <v>13.69</v>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="35">
         <v>17.54</v>
       </c>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
-      <c r="H50" s="33"/>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
-      <c r="L50" s="33"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="34"/>
+      <c r="H50" s="34"/>
+      <c r="I50" s="34"/>
+      <c r="J50" s="34"/>
+      <c r="K50" s="34"/>
+      <c r="L50" s="34"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="29" t="s">
-        <v>342</v>
-      </c>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
-      <c r="J51" s="30"/>
-      <c r="K51" s="30"/>
-      <c r="L51" s="30"/>
+      <c r="A51" s="30" t="s">
+        <v>343</v>
+      </c>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="31"/>
+      <c r="K51" s="31"/>
+      <c r="L51" s="31"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="31" t="s">
-        <v>343</v>
-      </c>
-      <c r="B52" s="33"/>
-      <c r="C52" s="34">
+      <c r="A52" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="B52" s="34"/>
+      <c r="C52" s="35">
         <v>10.73</v>
       </c>
-      <c r="D52" s="33"/>
-      <c r="E52" s="34">
+      <c r="D52" s="34"/>
+      <c r="E52" s="35">
         <v>45.76</v>
       </c>
-      <c r="F52" s="33"/>
-      <c r="G52" s="33"/>
-      <c r="H52" s="34">
+      <c r="F52" s="34"/>
+      <c r="G52" s="34"/>
+      <c r="H52" s="35">
         <v>57.27</v>
       </c>
-      <c r="I52" s="33"/>
-      <c r="J52" s="33"/>
-      <c r="K52" s="33"/>
-      <c r="L52" s="33"/>
+      <c r="I52" s="34"/>
+      <c r="J52" s="34"/>
+      <c r="K52" s="34"/>
+      <c r="L52" s="34"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="29" t="s">
-        <v>344</v>
-      </c>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="30"/>
-      <c r="I53" s="30"/>
-      <c r="J53" s="30"/>
-      <c r="K53" s="30"/>
-      <c r="L53" s="30"/>
+      <c r="A53" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="31"/>
+      <c r="J53" s="31"/>
+      <c r="K53" s="31"/>
+      <c r="L53" s="31"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="31" t="s">
-        <v>345</v>
-      </c>
-      <c r="B54" s="34">
+      <c r="A54" s="32" t="s">
+        <v>346</v>
+      </c>
+      <c r="B54" s="35">
         <v>46.59</v>
       </c>
-      <c r="C54" s="34">
+      <c r="C54" s="35">
         <v>8.73</v>
       </c>
-      <c r="D54" s="33"/>
-      <c r="E54" s="34">
+      <c r="D54" s="34"/>
+      <c r="E54" s="35">
         <v>29.01</v>
       </c>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="34">
+      <c r="F54" s="34"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="35">
         <v>57.27</v>
       </c>
-      <c r="I54" s="33"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="33"/>
-      <c r="L54" s="33"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="34"/>
+      <c r="K54" s="34"/>
+      <c r="L54" s="34"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="B55" s="34">
+      <c r="A55" s="32" t="s">
+        <v>347</v>
+      </c>
+      <c r="B55" s="35">
         <v>0.97</v>
       </c>
-      <c r="C55" s="34">
+      <c r="C55" s="35">
         <v>1.19</v>
       </c>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
-      <c r="F55" s="33"/>
-      <c r="G55" s="33"/>
-      <c r="H55" s="33"/>
-      <c r="I55" s="33"/>
-      <c r="J55" s="33"/>
-      <c r="K55" s="33"/>
-      <c r="L55" s="33"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="34"/>
+      <c r="L55" s="34"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="29" t="s">
-        <v>347</v>
-      </c>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-      <c r="G56" s="30"/>
-      <c r="H56" s="30"/>
-      <c r="I56" s="30"/>
-      <c r="J56" s="30"/>
-      <c r="K56" s="30"/>
-      <c r="L56" s="30"/>
+      <c r="A56" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="B56" s="31"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="31"/>
+      <c r="E56" s="31"/>
+      <c r="F56" s="31"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="31"/>
+      <c r="I56" s="31"/>
+      <c r="J56" s="31"/>
+      <c r="K56" s="31"/>
+      <c r="L56" s="31"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="31" t="s">
-        <v>348</v>
-      </c>
-      <c r="B57" s="33"/>
-      <c r="C57" s="34">
+      <c r="A57" s="32" t="s">
+        <v>349</v>
+      </c>
+      <c r="B57" s="34"/>
+      <c r="C57" s="35">
         <v>0.07</v>
       </c>
-      <c r="D57" s="33"/>
-      <c r="E57" s="34">
+      <c r="D57" s="34"/>
+      <c r="E57" s="35">
         <v>0.35</v>
       </c>
-      <c r="F57" s="33"/>
-      <c r="G57" s="33"/>
-      <c r="H57" s="34">
+      <c r="F57" s="34"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="35">
         <v>0.1</v>
       </c>
-      <c r="I57" s="33"/>
-      <c r="J57" s="33"/>
-      <c r="K57" s="33"/>
-      <c r="L57" s="33"/>
+      <c r="I57" s="34"/>
+      <c r="J57" s="34"/>
+      <c r="K57" s="34"/>
+      <c r="L57" s="34"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="29" t="s">
-        <v>349</v>
-      </c>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="30"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="30"/>
+      <c r="A58" s="30" t="s">
+        <v>350</v>
+      </c>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="31"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="31" t="s">
-        <v>350</v>
-      </c>
-      <c r="B59" s="34">
+      <c r="A59" s="32" t="s">
+        <v>351</v>
+      </c>
+      <c r="B59" s="35">
         <v>0.7</v>
       </c>
-      <c r="C59" s="34">
+      <c r="C59" s="35">
         <v>0.62</v>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="35">
         <v>1.19</v>
       </c>
-      <c r="E59" s="34">
+      <c r="E59" s="35">
         <v>2.06</v>
       </c>
-      <c r="F59" s="34">
+      <c r="F59" s="35">
         <v>8.93</v>
       </c>
-      <c r="G59" s="34">
+      <c r="G59" s="35">
         <v>4.75</v>
       </c>
-      <c r="H59" s="33"/>
-      <c r="I59" s="33"/>
-      <c r="J59" s="33"/>
-      <c r="K59" s="33"/>
-      <c r="L59" s="33"/>
+      <c r="H59" s="34"/>
+      <c r="I59" s="34"/>
+      <c r="J59" s="34"/>
+      <c r="K59" s="34"/>
+      <c r="L59" s="34"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="B60" s="34">
+      <c r="A60" s="32" t="s">
+        <v>352</v>
+      </c>
+      <c r="B60" s="35">
         <v>1.67</v>
       </c>
-      <c r="C60" s="34">
+      <c r="C60" s="35">
         <v>2.02</v>
       </c>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="33"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="33"/>
-      <c r="J60" s="33"/>
-      <c r="K60" s="33"/>
-      <c r="L60" s="33"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="34"/>
+      <c r="I60" s="34"/>
+      <c r="J60" s="34"/>
+      <c r="K60" s="34"/>
+      <c r="L60" s="34"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="29" t="s">
-        <v>352</v>
-      </c>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
+      <c r="A61" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="31"/>
+      <c r="K61" s="31"/>
+      <c r="L61" s="31"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="B62" s="34">
+      <c r="A62" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="B62" s="35">
         <v>3.59</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="35">
         <v>2.52</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="35">
         <v>4.68</v>
       </c>
-      <c r="E62" s="34">
+      <c r="E62" s="35">
         <v>4.71</v>
       </c>
-      <c r="F62" s="34">
+      <c r="F62" s="35">
         <v>50.83</v>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="33">
         <v>201.24</v>
       </c>
-      <c r="H62" s="33"/>
-      <c r="I62" s="33"/>
-      <c r="J62" s="33"/>
-      <c r="K62" s="33"/>
-      <c r="L62" s="33"/>
+      <c r="H62" s="34"/>
+      <c r="I62" s="34"/>
+      <c r="J62" s="34"/>
+      <c r="K62" s="34"/>
+      <c r="L62" s="34"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="B63" s="34">
+      <c r="A63" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="B63" s="35">
         <v>6.23</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="35">
         <v>7.14</v>
       </c>
-      <c r="D63" s="33"/>
-      <c r="E63" s="33"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="33"/>
-      <c r="L63" s="33"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="34"/>
+      <c r="I63" s="34"/>
+      <c r="J63" s="34"/>
+      <c r="K63" s="34"/>
+      <c r="L63" s="34"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="29" t="s">
-        <v>355</v>
-      </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="30"/>
-      <c r="J64" s="30"/>
-      <c r="K64" s="30"/>
-      <c r="L64" s="30"/>
+      <c r="A64" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B64" s="31"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="31"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="31"/>
+      <c r="K64" s="31"/>
+      <c r="L64" s="31"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="31" t="s">
-        <v>356</v>
-      </c>
-      <c r="B65" s="34">
+      <c r="A65" s="32" t="s">
+        <v>357</v>
+      </c>
+      <c r="B65" s="35">
         <v>6.14</v>
       </c>
-      <c r="C65" s="34">
+      <c r="C65" s="35">
         <v>2.92</v>
       </c>
-      <c r="D65" s="34">
+      <c r="D65" s="35">
         <v>5.93</v>
       </c>
-      <c r="E65" s="34">
+      <c r="E65" s="35">
         <v>24.43</v>
       </c>
-      <c r="F65" s="33"/>
-      <c r="G65" s="33"/>
-      <c r="H65" s="33"/>
-      <c r="I65" s="33"/>
-      <c r="J65" s="33"/>
-      <c r="K65" s="33"/>
-      <c r="L65" s="33"/>
+      <c r="F65" s="34"/>
+      <c r="G65" s="34"/>
+      <c r="H65" s="34"/>
+      <c r="I65" s="34"/>
+      <c r="J65" s="34"/>
+      <c r="K65" s="34"/>
+      <c r="L65" s="34"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="31" t="s">
-        <v>357</v>
-      </c>
-      <c r="B66" s="34">
+      <c r="A66" s="32" t="s">
+        <v>358</v>
+      </c>
+      <c r="B66" s="35">
         <v>13.27</v>
       </c>
-      <c r="C66" s="34">
+      <c r="C66" s="35">
         <v>16.3</v>
       </c>
-      <c r="D66" s="33"/>
-      <c r="E66" s="33"/>
-      <c r="F66" s="33"/>
-      <c r="G66" s="33"/>
-      <c r="H66" s="33"/>
-      <c r="I66" s="33"/>
-      <c r="J66" s="33"/>
-      <c r="K66" s="33"/>
-      <c r="L66" s="33"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="34"/>
+      <c r="H66" s="34"/>
+      <c r="I66" s="34"/>
+      <c r="J66" s="34"/>
+      <c r="K66" s="34"/>
+      <c r="L66" s="34"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="30"/>
-      <c r="K67" s="30"/>
-      <c r="L67" s="30"/>
+      <c r="A67" s="30" t="s">
+        <v>359</v>
+      </c>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="31" t="s">
-        <v>359</v>
-      </c>
-      <c r="B68" s="33"/>
-      <c r="C68" s="34">
+      <c r="A68" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="B68" s="34"/>
+      <c r="C68" s="35">
         <v>6.7</v>
       </c>
-      <c r="D68" s="34">
+      <c r="D68" s="35">
         <v>12.73</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="33">
         <v>720.58</v>
       </c>
-      <c r="F68" s="33"/>
-      <c r="G68" s="33"/>
-      <c r="H68" s="33"/>
-      <c r="I68" s="33"/>
-      <c r="J68" s="33"/>
-      <c r="K68" s="33"/>
-      <c r="L68" s="33"/>
+      <c r="F68" s="34"/>
+      <c r="G68" s="34"/>
+      <c r="H68" s="34"/>
+      <c r="I68" s="34"/>
+      <c r="J68" s="34"/>
+      <c r="K68" s="34"/>
+      <c r="L68" s="34"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="B69" s="33"/>
-      <c r="C69" s="32">
+      <c r="A69" s="32" t="s">
+        <v>361</v>
+      </c>
+      <c r="B69" s="34"/>
+      <c r="C69" s="33">
         <v>153.57</v>
       </c>
-      <c r="D69" s="33"/>
-      <c r="E69" s="33"/>
-      <c r="F69" s="33"/>
-      <c r="G69" s="33"/>
-      <c r="H69" s="33"/>
-      <c r="I69" s="33"/>
-      <c r="J69" s="33"/>
-      <c r="K69" s="33"/>
-      <c r="L69" s="33"/>
+      <c r="D69" s="34"/>
+      <c r="E69" s="34"/>
+      <c r="F69" s="34"/>
+      <c r="G69" s="34"/>
+      <c r="H69" s="34"/>
+      <c r="I69" s="34"/>
+      <c r="J69" s="34"/>
+      <c r="K69" s="34"/>
+      <c r="L69" s="34"/>
     </row>
     <row r="70" ht="15.75" customHeight="1"/>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/data/stx_xlsx/EG7.ST.xlsx
+++ b/data/stx_xlsx/EG7.ST.xlsx
@@ -537,187 +537,187 @@
     <t>Tangible non-current assets</t>
   </si>
   <si>
+    <t>Liabilities to credit institutions (Do not use)</t>
+  </si>
+  <si>
+    <t>Plant, Machinery &amp; Equipment - Gross</t>
+  </si>
+  <si>
+    <t>Machinery - Net - Balancing value</t>
+  </si>
+  <si>
+    <t>Equipment - Net</t>
+  </si>
+  <si>
+    <t>Right-of-use assets</t>
+  </si>
+  <si>
+    <t>Other intangible assets</t>
+  </si>
+  <si>
+    <t>Self-Generated Intangibles - Other - Gross</t>
+  </si>
+  <si>
+    <t>Self-Generated Intangibles - Other - Accumulated Amortization &amp; Impairment</t>
+  </si>
+  <si>
+    <t>Self-Generated Intangibles- Other - Net - Balancing value</t>
+  </si>
+  <si>
+    <t>IP Rights - Gross</t>
+  </si>
+  <si>
+    <t>IP Rights - Accumulated Amortization &amp; Impairment</t>
+  </si>
+  <si>
+    <t>IP Rights - Net - Balancing value</t>
+  </si>
+  <si>
+    <t>Customer Related Assets - Other - Gross</t>
+  </si>
+  <si>
+    <t>Customer Related Assets - Other - Accumulated Amortization &amp; Impairment</t>
+  </si>
+  <si>
+    <t>Intangible Assets - Other - Gross</t>
+  </si>
+  <si>
+    <t>Intangible Assets - Other - Accumulated Amortization &amp; Impairment</t>
+  </si>
+  <si>
+    <t>Intangible Assets - Other - Net - Balancing value</t>
+  </si>
+  <si>
+    <t>Intangible non-current assets - Balancing value</t>
+  </si>
+  <si>
+    <t>Gaming rights-gross</t>
+  </si>
+  <si>
+    <t>Gaming rights- Accumulated Amortization &amp; Impairment</t>
+  </si>
+  <si>
+    <t>Gaming rights- Net - Balancing value</t>
+  </si>
+  <si>
+    <t>Other non-current receivables</t>
+  </si>
+  <si>
+    <t>Deferred tax assets</t>
+  </si>
+  <si>
+    <t>Other Long Term Receivables</t>
+  </si>
+  <si>
+    <t>Balancing Item - Noncurrent Assets</t>
+  </si>
+  <si>
+    <t>Total Non-Current Assets</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>Inventories - Finished Goods</t>
+  </si>
+  <si>
+    <t>Current receivables</t>
+  </si>
+  <si>
+    <t>Accounts &amp; Notes Receivable - Trade - Gross</t>
+  </si>
+  <si>
+    <t>Provision - Doubtful Accounts</t>
+  </si>
+  <si>
+    <t>Current tax claim</t>
+  </si>
+  <si>
+    <t>Other Receivables</t>
+  </si>
+  <si>
+    <t>Accrued income</t>
+  </si>
+  <si>
+    <t>Prepayments and accrued income</t>
+  </si>
+  <si>
+    <t>Other prepaid expenses</t>
+  </si>
+  <si>
+    <t>Prepaid Expenses and Accrued Income - Balancing value</t>
+  </si>
+  <si>
+    <t>Cash and cash equivalents</t>
+  </si>
+  <si>
+    <t>Balancing Item - Current Assets</t>
+  </si>
+  <si>
+    <t>Total Current Assets</t>
+  </si>
+  <si>
+    <t>Balancing Item - Assets</t>
+  </si>
+  <si>
+    <t>Total Assets</t>
+  </si>
+  <si>
+    <t>Share capital</t>
+  </si>
+  <si>
+    <t>Other contributed capital</t>
+  </si>
+  <si>
+    <t>Retained Earnings</t>
+  </si>
+  <si>
+    <t>Reserves</t>
+  </si>
+  <si>
+    <t>Retained earnings including profit for the period</t>
+  </si>
+  <si>
+    <t>Balancing Item - Shareholders Equity</t>
+  </si>
+  <si>
+    <t>Equity attributable to the parent companys shareholders</t>
+  </si>
+  <si>
+    <t>Balancing Item - Total Equity</t>
+  </si>
+  <si>
+    <t>Total Equity</t>
+  </si>
+  <si>
+    <t>Non-current liabilities</t>
+  </si>
+  <si>
+    <t>Bond Loans</t>
+  </si>
+  <si>
+    <t>Deferred tax liability</t>
+  </si>
+  <si>
+    <t>Contingent Consideration</t>
+  </si>
+  <si>
+    <t>Contract Liabilities - Long-Term - Advance Consideration &amp; Progress Billings in Excess of Unbilled Revenue</t>
+  </si>
+  <si>
+    <t>Other liabilities</t>
+  </si>
+  <si>
+    <t>Provisions</t>
+  </si>
+  <si>
+    <t>Balancing Item - Noncurrent Liabilities</t>
+  </si>
+  <si>
+    <t>Total non-current liabilities</t>
+  </si>
+  <si>
     <t>Liabilities to credit institutions</t>
-  </si>
-  <si>
-    <t>Plant, Machinery &amp; Equipment - Gross</t>
-  </si>
-  <si>
-    <t>Machinery - Net - Balancing value</t>
-  </si>
-  <si>
-    <t>Equipment - Net</t>
-  </si>
-  <si>
-    <t>Right-of-use assets</t>
-  </si>
-  <si>
-    <t>Other intangible assets</t>
-  </si>
-  <si>
-    <t>Self-Generated Intangibles - Other - Gross</t>
-  </si>
-  <si>
-    <t>Self-Generated Intangibles - Other - Accumulated Amortization &amp; Impairment</t>
-  </si>
-  <si>
-    <t>Self-Generated Intangibles- Other - Net - Balancing value</t>
-  </si>
-  <si>
-    <t>IP Rights - Gross</t>
-  </si>
-  <si>
-    <t>IP Rights - Accumulated Amortization &amp; Impairment</t>
-  </si>
-  <si>
-    <t>IP Rights - Net - Balancing value</t>
-  </si>
-  <si>
-    <t>Customer Related Assets - Other - Gross</t>
-  </si>
-  <si>
-    <t>Customer Related Assets - Other - Accumulated Amortization &amp; Impairment</t>
-  </si>
-  <si>
-    <t>Intangible Assets - Other - Gross</t>
-  </si>
-  <si>
-    <t>Intangible Assets - Other - Accumulated Amortization &amp; Impairment</t>
-  </si>
-  <si>
-    <t>Intangible Assets - Other - Net - Balancing value</t>
-  </si>
-  <si>
-    <t>Intangible non-current assets - Balancing value</t>
-  </si>
-  <si>
-    <t>Gaming rights-gross</t>
-  </si>
-  <si>
-    <t>Gaming rights- Accumulated Amortization &amp; Impairment</t>
-  </si>
-  <si>
-    <t>Gaming rights- Net - Balancing value</t>
-  </si>
-  <si>
-    <t>Other non-current receivables</t>
-  </si>
-  <si>
-    <t>Deferred tax assets</t>
-  </si>
-  <si>
-    <t>Other Long Term Receivables</t>
-  </si>
-  <si>
-    <t>Balancing Item - Noncurrent Assets</t>
-  </si>
-  <si>
-    <t>Total Non-Current Assets</t>
-  </si>
-  <si>
-    <t>Inventory</t>
-  </si>
-  <si>
-    <t>Inventories - Finished Goods</t>
-  </si>
-  <si>
-    <t>Current receivables</t>
-  </si>
-  <si>
-    <t>Accounts &amp; Notes Receivable - Trade - Gross</t>
-  </si>
-  <si>
-    <t>Provision - Doubtful Accounts</t>
-  </si>
-  <si>
-    <t>Current tax claim</t>
-  </si>
-  <si>
-    <t>Other Receivables</t>
-  </si>
-  <si>
-    <t>Accrued income</t>
-  </si>
-  <si>
-    <t>Prepayments and accrued income</t>
-  </si>
-  <si>
-    <t>Other prepaid expenses</t>
-  </si>
-  <si>
-    <t>Prepaid Expenses and Accrued Income - Balancing value</t>
-  </si>
-  <si>
-    <t>Cash and cash equivalents</t>
-  </si>
-  <si>
-    <t>Balancing Item - Current Assets</t>
-  </si>
-  <si>
-    <t>Total Current Assets</t>
-  </si>
-  <si>
-    <t>Balancing Item - Assets</t>
-  </si>
-  <si>
-    <t>Total Assets</t>
-  </si>
-  <si>
-    <t>Share capital</t>
-  </si>
-  <si>
-    <t>Other contributed capital</t>
-  </si>
-  <si>
-    <t>Retained Earnings</t>
-  </si>
-  <si>
-    <t>Reserves</t>
-  </si>
-  <si>
-    <t>Retained earnings including profit for the period</t>
-  </si>
-  <si>
-    <t>Balancing Item - Shareholders Equity</t>
-  </si>
-  <si>
-    <t>Equity attributable to the parent companys shareholders</t>
-  </si>
-  <si>
-    <t>Balancing Item - Total Equity</t>
-  </si>
-  <si>
-    <t>Total Equity</t>
-  </si>
-  <si>
-    <t>Non-current liabilities</t>
-  </si>
-  <si>
-    <t>Bond Loans</t>
-  </si>
-  <si>
-    <t>Liabilities to credit institutions (Do not use)</t>
-  </si>
-  <si>
-    <t>Deferred tax liability</t>
-  </si>
-  <si>
-    <t>Contingent Consideration</t>
-  </si>
-  <si>
-    <t>Contract Liabilities - Long-Term - Advance Consideration &amp; Progress Billings in Excess of Unbilled Revenue</t>
-  </si>
-  <si>
-    <t>Other liabilities</t>
-  </si>
-  <si>
-    <t>Provisions</t>
-  </si>
-  <si>
-    <t>Balancing Item - Noncurrent Liabilities</t>
-  </si>
-  <si>
-    <t>Total non-current liabilities</t>
   </si>
   <si>
     <t>Accounts payable</t>
@@ -6652,7 +6652,7 @@
       <c r="M24" s="22"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="29" t="s">
         <v>172</v>
       </c>
       <c r="B25" s="22"/>
@@ -6708,7 +6708,7 @@
       <c r="M26" s="22"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="29" t="s">
         <v>172</v>
       </c>
       <c r="B27" s="22"/>
@@ -8243,7 +8243,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="29" t="s">
-        <v>225</v>
+        <v>172</v>
       </c>
       <c r="B81" s="15">
         <v>379.32</v>
@@ -8305,7 +8305,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B83" s="16">
         <v>87.15</v>
@@ -8338,7 +8338,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B84" s="16">
         <v>85.95</v>
@@ -8369,7 +8369,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B85" s="22"/>
       <c r="C85" s="16">
@@ -8398,7 +8398,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B86" s="16">
         <v>2.95</v>
@@ -8429,7 +8429,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B87" s="22"/>
       <c r="C87" s="22"/>
@@ -8448,7 +8448,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B88" s="16">
         <v>0.11</v>
@@ -8473,7 +8473,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B89" s="18">
         <v>592.77</v>
@@ -8514,7 +8514,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>172</v>
+        <v>232</v>
       </c>
       <c r="B90" s="16">
         <v>0.55</v>
@@ -8537,7 +8537,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>172</v>
+        <v>232</v>
       </c>
       <c r="B91" s="22"/>
       <c r="C91" s="22"/>
